--- a/Notes and data for listed articles/(row 5) data for 2023 Miao et al./raw_data/data_for_discrimination_index.xlsx
+++ b/Notes and data for listed articles/(row 5) data for 2023 Miao et al./raw_data/data_for_discrimination_index.xlsx
@@ -96,7 +96,7 @@
     <xdr:ext cx="3200400" cy="3028950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -124,7 +124,7 @@
     <xdr:ext cx="3905250" cy="2371725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Notes and data for listed articles/(row 5) data for 2023 Miao et al./raw_data/data_for_discrimination_index.xlsx
+++ b/Notes and data for listed articles/(row 5) data for 2023 Miao et al./raw_data/data_for_discrimination_index.xlsx
@@ -96,7 +96,7 @@
     <xdr:ext cx="3200400" cy="3028950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -124,7 +124,7 @@
     <xdr:ext cx="3905250" cy="2371725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
